--- a/www/download/IND.surplus_value.empe_ls.r.pc.rpO1.xlsx
+++ b/www/download/IND.surplus_value.empe_ls.r.pc.rpO1.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>441.24</t>
+          <t>4.41238371342967</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>426.07</t>
+          <t>4.26071902806431</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>413.7</t>
+          <t>4.13697637208657</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>412.2</t>
+          <t>4.12198307133199</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>429.25</t>
+          <t>4.29254907670131</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>420.88</t>
+          <t>4.20878689731965</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>408.08</t>
+          <t>4.08077779766229</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>416.32</t>
+          <t>4.16317600059071</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>4.31001130059648</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>417.73</t>
+          <t>4.1773340261804</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>423.88</t>
+          <t>4.23881964485114</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>413.38</t>
+          <t>4.13383375038341</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>401.6</t>
+          <t>4.01600015476829</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>389.26</t>
+          <t>3.89263780830498</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>379.24</t>
+          <t>3.79244090207236</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>524.38</t>
+          <t>5.24378722941684</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>508.01</t>
+          <t>5.08012188124394</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>491.04</t>
+          <t>4.91036392966687</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>497.68</t>
+          <t>4.97678229456568</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>521.54</t>
+          <t>5.21540781696164</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>508.69</t>
+          <t>5.08689869775253</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>496.49</t>
+          <t>4.96494851241462</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>504.41</t>
+          <t>5.04410939760999</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>383.68</t>
+          <t>3.8367754838327</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>506.37</t>
+          <t>5.0636868681499</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>509.12</t>
+          <t>5.09117307214755</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>502.14</t>
+          <t>5.02143297128475</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>525.34</t>
+          <t>5.25339301566475</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>540.64</t>
+          <t>5.40643793360468</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>533.1</t>
+          <t>5.33102331480262</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>394.42</t>
+          <t>3.94418555503487</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>381.06</t>
+          <t>3.81062177653024</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>369.9</t>
+          <t>3.69900892123677</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>368.99</t>
+          <t>3.68994216291272</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>381.44</t>
+          <t>3.81441326369094</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>377.8</t>
+          <t>3.7780154673907</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>364.87</t>
+          <t>3.64872243474893</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>369.6</t>
+          <t>3.69599951665393</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>324.43</t>
+          <t>3.24431590394185</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>376.62</t>
+          <t>3.76618260046368</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>380.71</t>
+          <t>3.80706114779189</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>374.63</t>
+          <t>3.74634107785552</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>379.83</t>
+          <t>3.79826712027306</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>366.06</t>
+          <t>3.66055800901203</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>358.08</t>
+          <t>3.5808257743217</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>410.52</t>
+          <t>4.10516369415221</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>394.94</t>
+          <t>3.94941141404713</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>378.07</t>
+          <t>3.7806581438858</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>374.03</t>
+          <t>3.74025683563675</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>394.49</t>
+          <t>3.94485942418349</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>387.2</t>
+          <t>3.87198060405639</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>375.15</t>
+          <t>3.75153697992074</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>384.3</t>
+          <t>3.84295627282676</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>328.84</t>
+          <t>3.28840705937563</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>394.26</t>
+          <t>3.94260577852254</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>399.01</t>
+          <t>3.99009828177986</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>390.47</t>
+          <t>3.90471309157344</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>375.61</t>
+          <t>3.75613605986404</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>365.27</t>
+          <t>3.65271607930556</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>359.02</t>
+          <t>3.59024377895773</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>630.63</t>
+          <t>6.30626924312538</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>609.39</t>
+          <t>6.09392366109493</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>591.19</t>
+          <t>5.9119080919902</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>588.06</t>
+          <t>5.88058080856142</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>610.66</t>
+          <t>6.10656062273012</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>586.79</t>
+          <t>5.86793945936931</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>569.98</t>
+          <t>5.69977242116771</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>580.61</t>
+          <t>5.80610489223123</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>591.32</t>
+          <t>5.91319139038006</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>562.42</t>
+          <t>5.62416823438461</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>560.43</t>
+          <t>5.60427711573707</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>546.65</t>
+          <t>5.46648260985424</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>530.92</t>
+          <t>5.30923432744783</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>510.71</t>
+          <t>5.10709294328622</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>491.95</t>
+          <t>4.91947910642274</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>4.42999205376449</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>438.95</t>
+          <t>4.38950702634433</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>414.28</t>
+          <t>4.14284783053936</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>417.37</t>
+          <t>4.17367420470756</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>443.72</t>
+          <t>4.43723541334876</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>432.64</t>
+          <t>4.32637615344643</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>421.1</t>
+          <t>4.21100815305403</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>439.42</t>
+          <t>4.39421271948619</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>460.76</t>
+          <t>4.60757761069125</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>447.15</t>
+          <t>4.47154374267452</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>456.73</t>
+          <t>4.56728480204403</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>443.2</t>
+          <t>4.43197364163068</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>433.68</t>
+          <t>4.33684097548733</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>428.36</t>
+          <t>4.28356678056438</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>422.74</t>
+          <t>4.22738979181152</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>357.09</t>
+          <t>3.57094520531778</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>345.5</t>
+          <t>3.45498268584879</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>336.3</t>
+          <t>3.3630184308981</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>336.44</t>
+          <t>3.364371325613</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>353.22</t>
+          <t>3.53215744864854</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>347.92</t>
+          <t>3.47924851591355</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>339.23</t>
+          <t>3.39231592981838</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>349.14</t>
+          <t>3.49143297130427</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>362.35</t>
+          <t>3.62349871281538</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>346.86</t>
+          <t>3.46858369746528</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>352.97</t>
+          <t>3.52965718885165</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>346.41</t>
+          <t>3.46414881279764</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>334.75</t>
+          <t>3.34752539671323</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>325.49</t>
+          <t>3.25489932445691</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>317.09</t>
+          <t>3.17090296663994</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>463.77</t>
+          <t>4.63769935620284</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>445.13</t>
+          <t>4.45126249273082</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>424.93</t>
+          <t>4.24928487828574</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>413.23</t>
+          <t>4.13225107426169</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>426.7</t>
+          <t>4.26700599823759</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>420.25</t>
+          <t>4.20252124610983</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>408.99</t>
+          <t>4.08989219442423</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>417.9</t>
+          <t>4.17898913672983</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>364.81</t>
+          <t>3.64810458586566</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>416.23</t>
+          <t>4.16230303964564</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>415.14</t>
+          <t>4.15135733724456</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>402.01</t>
+          <t>4.0201102978184</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>400.81</t>
+          <t>4.00813841350074</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>371.8</t>
+          <t>3.71799126831701</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>359.26</t>
+          <t>3.59263552013344</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>536.1</t>
+          <t>5.36102375492929</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>516.99</t>
+          <t>5.16991180805429</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>500.97</t>
+          <t>5.00974051583568</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>498.09</t>
+          <t>4.98087297265841</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>518.91</t>
+          <t>5.18906729335485</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>496.87</t>
+          <t>4.96865803337858</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>495.62</t>
+          <t>4.95620396455583</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>488.71</t>
+          <t>4.88709857617956</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>321.59</t>
+          <t>3.21589946990114</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>493.55</t>
+          <t>4.93550294246445</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>498.13</t>
+          <t>4.98126868062112</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>487.87</t>
+          <t>4.87873644918664</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>440.2</t>
+          <t>4.40203306039173</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>412.65</t>
+          <t>4.12654453121714</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>408.95</t>
+          <t>4.08950807357457</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>601.48</t>
+          <t>6.01476844551256</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>591.72</t>
+          <t>5.9171650798934</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>579.55</t>
+          <t>5.79546973034248</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>573.8</t>
+          <t>5.7379763035876</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>583.68</t>
+          <t>5.83678195602146</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>576.34</t>
+          <t>5.76338889254493</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>552.16</t>
+          <t>5.52164746140459</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>5.5800404063178</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>572.88</t>
+          <t>5.72880453221714</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>604.03</t>
+          <t>6.04031920204021</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>577.23</t>
+          <t>5.77234630369919</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>569.59</t>
+          <t>5.69589230662807</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>544.94</t>
+          <t>5.44936481183272</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>548.47</t>
+          <t>5.48470779942033</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>554.22</t>
+          <t>5.54224664212299</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>454.1</t>
+          <t>4.54095231861334</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>438.33</t>
+          <t>4.38334056873997</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>422.32</t>
+          <t>4.22320728369688</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>424.26</t>
+          <t>4.2425939410015</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>443.68</t>
+          <t>4.43678288065485</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>437.14</t>
+          <t>4.37140094982723</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>425.71</t>
+          <t>4.25714375530887</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>431.67</t>
+          <t>4.31671695327958</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>464.48</t>
+          <t>4.64478519716545</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>457.06</t>
+          <t>4.57061840286839</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>450.74</t>
+          <t>4.50744364770818</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>457.01</t>
+          <t>4.57010207091904</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>405.98</t>
+          <t>4.0598146766544</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>392.4</t>
+          <t>3.92395892219321</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>377.48</t>
+          <t>3.77482751738524</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>421.2</t>
+          <t>4.21199875619531</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>409.47</t>
+          <t>4.09469288783092</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>397.56</t>
+          <t>3.97564332338671</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>396.09</t>
+          <t>3.96094053271563</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>413.44</t>
+          <t>4.13440824049495</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>405.32</t>
+          <t>4.05322419482654</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>395.14</t>
+          <t>3.95135133397012</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>405.03</t>
+          <t>4.05032197886166</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>3.6300228778337</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>402.34</t>
+          <t>4.0233670447669</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>406.35</t>
+          <t>4.06353625501771</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>393.37</t>
+          <t>3.93369077624999</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>376.75</t>
+          <t>3.76750307051953</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>365.89</t>
+          <t>3.65893958355439</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>361.55</t>
+          <t>3.61552116717221</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>592.35</t>
+          <t>5.92354875802043</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>565.91</t>
+          <t>5.65910304181744</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>541.78</t>
+          <t>5.41777403395044</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>529.58</t>
+          <t>5.29579146389778</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>557.94</t>
+          <t>5.57935301528972</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>548.13</t>
+          <t>5.48126824209407</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>527.88</t>
+          <t>5.27877468564589</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>532.41</t>
+          <t>5.32406791082601</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>370.57</t>
+          <t>3.70571207310415</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>505.75</t>
+          <t>5.05750559565414</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>500.45</t>
+          <t>5.00452187558226</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>467.7</t>
+          <t>4.67700378368278</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>383.1</t>
+          <t>3.83101026007922</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>330.83</t>
+          <t>3.30829984021629</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>338.8</t>
+          <t>3.38803470376007</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>378.53</t>
+          <t>3.78532468142869</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>365.9</t>
+          <t>3.65899280446743</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>3.54995305841975</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>366.8</t>
+          <t>3.66797645143484</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>391.5</t>
+          <t>3.91500973482951</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>387.24</t>
+          <t>3.87239981681386</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>373.02</t>
+          <t>3.73022859790123</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>383.07</t>
+          <t>3.83074144811753</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>361.3</t>
+          <t>3.61299740761919</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>385.98</t>
+          <t>3.85979601930165</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>390.92</t>
+          <t>3.90923775863507</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>381.71</t>
+          <t>3.81713966465351</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>362.54</t>
+          <t>3.62544797205678</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>343.23</t>
+          <t>3.43233979041224</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>334.91</t>
+          <t>3.34905437804344</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>456.43</t>
+          <t>4.56427659086556</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>448.17</t>
+          <t>4.48170934400427</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>425.39</t>
+          <t>4.25394504904076</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>420.06</t>
+          <t>4.20060202720066</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>440.51</t>
+          <t>4.40512082702045</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>429.8</t>
+          <t>4.29798848120359</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>417.79</t>
+          <t>4.17788443964869</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>417.32</t>
+          <t>4.17318876859861</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>341.77</t>
+          <t>3.4176727513367</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>410.71</t>
+          <t>4.10708634845003</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>411.02</t>
+          <t>4.11019172777077</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>398.76</t>
+          <t>3.9876463828031</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>396.35</t>
+          <t>3.96350147479619</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>382.2</t>
+          <t>3.82204301430594</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>374.65</t>
+          <t>3.74648778744976</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>457.04</t>
+          <t>4.57035638785739</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>442.58</t>
+          <t>4.42580421164948</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>437.09</t>
+          <t>4.37093788018888</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>447.1</t>
+          <t>4.47104273440305</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>463.15</t>
+          <t>4.63151235884164</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>454.62</t>
+          <t>4.54623143238691</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>436.21</t>
+          <t>4.36209560749529</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>441.37</t>
+          <t>4.41371008419632</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>459.08</t>
+          <t>4.59084327875404</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>443.87</t>
+          <t>4.43867213638736</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>447.64</t>
+          <t>4.47643907813903</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>439.29</t>
+          <t>4.39289625973844</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>427.81</t>
+          <t>4.27814230015979</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>416.85</t>
+          <t>4.16847857277338</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>406.02</t>
+          <t>4.06022792386811</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>343.67</t>
+          <t>3.43665069953449</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>340.29</t>
+          <t>3.40291044537266</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>338.39</t>
+          <t>3.38392544335805</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>346.94</t>
+          <t>3.46941251081674</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>375.61</t>
+          <t>3.75614770647885</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>383.28</t>
+          <t>3.83282929878973</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>371.11</t>
+          <t>3.71109853304797</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>381.48</t>
+          <t>3.8147945859022</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>336.2</t>
+          <t>3.36200040280763</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>376.25</t>
+          <t>3.76245814944643</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>375.24</t>
+          <t>3.75235114187467</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>363.62</t>
+          <t>3.63616815257528</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>355.79</t>
+          <t>3.55790787097072</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>334.58</t>
+          <t>3.34577510876396</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>326.07</t>
+          <t>3.26070870290588</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>529.74</t>
+          <t>5.29737851537361</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>511.65</t>
+          <t>5.11652018230601</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>496.25</t>
+          <t>4.96250160541812</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>495.02</t>
+          <t>4.95018120659266</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>538.73</t>
+          <t>5.3872863359848</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>514.31</t>
+          <t>5.14307582314013</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>492.54</t>
+          <t>4.92543703317205</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>496.73</t>
+          <t>4.96731165464197</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>294.43</t>
+          <t>2.94432608057651</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>519.96</t>
+          <t>5.19957326623537</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>531.61</t>
+          <t>5.31613823159505</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>522.44</t>
+          <t>5.22440616337318</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>495.38</t>
+          <t>4.95378996226389</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>516.75</t>
+          <t>5.16745445393949</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>515.29</t>
+          <t>5.15294595454545</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>471.75</t>
+          <t>4.71750317417035</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>436.25</t>
+          <t>4.36246114501878</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>433.96</t>
+          <t>4.33962582453568</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>423.31</t>
+          <t>4.23306258286777</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>423.41</t>
+          <t>4.23414640497838</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>420.79</t>
+          <t>4.20794281932983</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>413.06</t>
+          <t>4.13055399792553</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>424.31</t>
+          <t>4.24308848645018</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>434.94</t>
+          <t>4.34935543319553</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>429.13</t>
+          <t>4.29133508365985</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>437.65</t>
+          <t>4.37653298637657</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>428.21</t>
+          <t>4.28212629615926</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>444.18</t>
+          <t>4.44183954116266</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>428.88</t>
+          <t>4.2888229552785</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>416.56</t>
+          <t>4.16562290199272</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>449.25</t>
+          <t>4.49254863651911</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>430.51</t>
+          <t>4.30508769914675</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>416.12</t>
+          <t>4.16119011591032</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>414.78</t>
+          <t>4.14779765764281</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>430.19</t>
+          <t>4.3018657952424</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>429.53</t>
+          <t>4.29531930393404</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>420.57</t>
+          <t>4.20568254656947</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>434.33</t>
+          <t>4.34325065162572</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>454.99</t>
+          <t>4.54987984769947</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>442.38</t>
+          <t>4.4238077722342</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>442.11</t>
+          <t>4.42113303644234</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>431.12</t>
+          <t>4.31115689985104</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>418.3</t>
+          <t>4.1829701208543</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>405.7</t>
+          <t>4.05700644786553</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>394.95</t>
+          <t>3.94951705929536</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>387.76</t>
+          <t>3.87764476935004</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>390.12</t>
+          <t>3.90123913918207</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>388.51</t>
+          <t>3.88511116588813</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>402.08</t>
+          <t>4.02076578463386</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>432.61</t>
+          <t>4.32607073254935</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>430.54</t>
+          <t>4.3054038439634</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>421.78</t>
+          <t>4.21778066100684</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>434.97</t>
+          <t>4.34971032439722</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>452.03</t>
+          <t>4.52030556507224</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>434.88</t>
+          <t>4.34876365914567</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>415.64</t>
+          <t>4.15642040404936</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>458.96</t>
+          <t>4.58957865596095</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>404.57</t>
+          <t>4.04567707623762</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>393.58</t>
+          <t>3.93580701645035</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>397.18</t>
+          <t>3.9718420620699</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>368.41</t>
+          <t>3.68409591460728</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>365.61</t>
+          <t>3.65614572113818</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>3.66000127677832</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>378.34</t>
+          <t>3.78343171154232</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>395.94</t>
+          <t>3.95943500618947</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>392.89</t>
+          <t>3.92890616550758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>379.98</t>
+          <t>3.79977115751858</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>389.99</t>
+          <t>3.89987825585091</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>344.17</t>
+          <t>3.44168052034057</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>388.27</t>
+          <t>3.88273726861926</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>392.61</t>
+          <t>3.92614463309818</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>382.36</t>
+          <t>3.82357549101438</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>366.3</t>
+          <t>3.66296297891585</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>339.39</t>
+          <t>3.3938975950013</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>330.78</t>
+          <t>3.30780732215884</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>411.3</t>
+          <t>4.11301429318554</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>402.11</t>
+          <t>4.02109147827699</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>385.32</t>
+          <t>3.85320577588315</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>387.52</t>
+          <t>3.87521741868413</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>397.27</t>
+          <t>3.97268318439732</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>387.13</t>
+          <t>3.87125872756923</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>379.98</t>
+          <t>3.79978029013289</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>394.48</t>
+          <t>3.94477265889815</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>403.75</t>
+          <t>4.03745119846494</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>401.43</t>
+          <t>4.0142858679098</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>411.5</t>
+          <t>4.11496000341061</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>402.01</t>
+          <t>4.02010471328591</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>390.98</t>
+          <t>3.90975299004102</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>379.77</t>
+          <t>3.79774270896495</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>372.62</t>
+          <t>3.72618256355103</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>456.99</t>
+          <t>4.56993883100061</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>456.33</t>
+          <t>4.5633389210653</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>444.25</t>
+          <t>4.44251781670852</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>456.64</t>
+          <t>4.56643677836922</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>458.21</t>
+          <t>4.58211601465838</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>452.05</t>
+          <t>4.52049761224294</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>471.48</t>
+          <t>4.71482974825997</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>489.7</t>
+          <t>4.89702406907653</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>517.57</t>
+          <t>5.17570606148939</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>511.43</t>
+          <t>5.11426726659356</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>510.92</t>
+          <t>5.10921025009616</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>499.25</t>
+          <t>4.99250717361609</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>486.71</t>
+          <t>4.86711457192435</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>472.78</t>
+          <t>4.72780146682525</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>460.74</t>
+          <t>4.6073613456249</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>504.01</t>
+          <t>5.04013949888706</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>484.23</t>
+          <t>4.84225191806003</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>463.03</t>
+          <t>4.63030335783053</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>457.48</t>
+          <t>4.57475407891353</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>478.71</t>
+          <t>4.78705305413889</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>475.39</t>
+          <t>4.75390869055851</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>457.81</t>
+          <t>4.578132647658</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>466.94</t>
+          <t>4.66942876828598</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>363.74</t>
+          <t>3.63737388381241</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>462.04</t>
+          <t>4.6204334626355</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>465.17</t>
+          <t>4.6516853555336</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>450.07</t>
+          <t>4.5006711883945</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>357.35</t>
+          <t>3.57348468081259</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>322.09</t>
+          <t>3.22089283381794</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>305.22</t>
+          <t>3.05218107407059</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>384.76</t>
+          <t>3.84762863177433</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>369.94</t>
+          <t>3.69937206792448</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>360.29</t>
+          <t>3.60288290614853</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>382.69</t>
+          <t>3.82693294227217</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>427.8</t>
+          <t>4.27795449283698</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>449.38</t>
+          <t>4.49375856035463</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>436.02</t>
+          <t>4.36018689513699</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>440.74</t>
+          <t>4.40737659707515</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>325.5</t>
+          <t>3.25498867090187</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>437.31</t>
+          <t>4.3731081163602</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>438.09</t>
+          <t>4.38094244592787</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>419.49</t>
+          <t>4.19488111199643</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>413.58</t>
+          <t>4.1358050824169</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>407.14</t>
+          <t>4.0713550944451</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>431.5</t>
+          <t>4.31499252988578</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>496.24</t>
+          <t>4.96242418401891</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>473.54</t>
+          <t>4.7353884166364</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>454.12</t>
+          <t>4.5412078751961</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>447.78</t>
+          <t>4.47779727324192</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>470.51</t>
+          <t>4.70505161374668</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>466.52</t>
+          <t>4.66524473479629</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>446.21</t>
+          <t>4.46205515109309</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>455.54</t>
+          <t>4.55538142290059</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>329.36</t>
+          <t>3.29363015566682</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>455.01</t>
+          <t>4.55006143954577</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>448.48</t>
+          <t>4.48478197009891</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>420.16</t>
+          <t>4.20158511032547</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>413.33</t>
+          <t>4.13329970810126</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>401.07</t>
+          <t>4.01066553300597</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>420.61</t>
+          <t>4.20611993175229</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>675.25</t>
+          <t>6.75252768420456</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>666.61</t>
+          <t>6.66608728299208</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>652.55</t>
+          <t>6.52551946013219</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>654.57</t>
+          <t>6.5457035613667</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>678.7</t>
+          <t>6.78698750105702</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>667.19</t>
+          <t>6.67185762817276</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>655.54</t>
+          <t>6.55540673067109</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>670.58</t>
+          <t>6.70582058898323</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>693.93</t>
+          <t>6.93927226117012</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>673.11</t>
+          <t>6.73105678440931</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>681.62</t>
+          <t>6.81618199246866</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>699.33</t>
+          <t>6.99329100778578</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>692.68</t>
+          <t>6.92675536234796</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>692.46</t>
+          <t>6.92462451234584</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>668.82</t>
+          <t>6.6881776404063</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>417.19</t>
+          <t>4.17194076795801</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>403.45</t>
+          <t>4.0344805652623</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>385.62</t>
+          <t>3.85620243000618</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>377.75</t>
+          <t>3.7775279781559</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>396.63</t>
+          <t>3.96628842922066</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>388.97</t>
+          <t>3.88967311378555</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>3.77003563977038</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>385.57</t>
+          <t>3.85570483584832</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>331.08</t>
+          <t>3.31084124416792</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>396.46</t>
+          <t>3.96458954930843</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>404.16</t>
+          <t>4.04155691123138</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>398.4</t>
+          <t>3.98398675832106</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>384.42</t>
+          <t>3.84417571014814</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>368.48</t>
+          <t>3.68478835107927</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>366.05</t>
+          <t>3.6604503255125</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>432.88</t>
+          <t>4.32878246667599</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>423.93</t>
+          <t>4.23932385153359</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>416.6</t>
+          <t>4.16602756730542</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>419.9</t>
+          <t>4.19896596946922</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>446.87</t>
+          <t>4.46868170283391</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>431.71</t>
+          <t>4.31707669470152</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>416.84</t>
+          <t>4.16839166049094</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>438.88</t>
+          <t>4.38876979404761</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>367.66</t>
+          <t>3.6766391391069</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>449.02</t>
+          <t>4.49019062773815</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>454.64</t>
+          <t>4.54642918311654</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>443.51</t>
+          <t>4.43506187226697</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>421.53</t>
+          <t>4.21527999483203</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>404.86</t>
+          <t>4.04863970672779</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>393.94</t>
+          <t>3.9393863580278</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>528.48</t>
+          <t>5.28481800716906</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>510.66</t>
+          <t>5.10659979616198</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>497.09</t>
+          <t>4.97085159114657</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>494.8</t>
+          <t>4.94795294956956</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>515.43</t>
+          <t>5.15434257078814</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>505.46</t>
+          <t>5.05464021290778</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>501.45</t>
+          <t>5.01447564258073</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>524.09</t>
+          <t>5.24087168504369</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>345.71</t>
+          <t>3.45713800137895</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>538.44</t>
+          <t>5.38436988170693</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>532.76</t>
+          <t>5.32760339865991</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>522.1</t>
+          <t>5.22101964018991</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>522.02</t>
+          <t>5.22023782820005</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>467.26</t>
+          <t>4.67261629186158</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>458.51</t>
+          <t>4.58511246440074</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>420.98</t>
+          <t>4.20982471029841</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>407.09</t>
+          <t>4.07092470980872</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>388.64</t>
+          <t>3.88644519423826</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>380.21</t>
+          <t>3.8020526829658</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>399.44</t>
+          <t>3.99442030894116</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>391.1</t>
+          <t>3.91097193658632</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>378.68</t>
+          <t>3.78678284953603</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>387.39</t>
+          <t>3.87388149074684</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>330.33</t>
+          <t>3.30334993936635</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>397.25</t>
+          <t>3.97250777734224</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>402.81</t>
+          <t>4.02812494567278</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>395.24</t>
+          <t>3.95237372169596</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>380.13</t>
+          <t>3.80132305229407</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>366.66</t>
+          <t>3.66657638101008</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>362.09</t>
+          <t>3.6208612019991</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>408.09</t>
+          <t>4.08089747068213</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>392.47</t>
+          <t>3.92473506200288</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>377.04</t>
+          <t>3.77041796711223</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>369.14</t>
+          <t>3.69141068747143</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>392.7</t>
+          <t>3.92701072670943</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>382.36</t>
+          <t>3.82364524772914</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>368.76</t>
+          <t>3.68757270362778</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>378.52</t>
+          <t>3.78522071502542</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>331.74</t>
+          <t>3.31737519301807</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>386.01</t>
+          <t>3.86014493172091</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>391.58</t>
+          <t>3.91579574248274</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>384.19</t>
+          <t>3.84191165089721</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>369.42</t>
+          <t>3.69424371365201</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>358.87</t>
+          <t>3.58869124029183</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>352.99</t>
+          <t>3.52989015685135</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>570.07</t>
+          <t>5.70070925680668</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>553.07</t>
+          <t>5.53070195669677</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>536.15</t>
+          <t>5.36153752060066</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>5.37996017116011</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>555.88</t>
+          <t>5.55878862692698</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>5.37000621982017</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>534.27</t>
+          <t>5.3427374930302</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>534.15</t>
+          <t>5.34150316678077</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>555.05</t>
+          <t>5.55048254019147</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>548.32</t>
+          <t>5.48324787681713</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>551.87</t>
+          <t>5.51873832047927</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>541.81</t>
+          <t>5.41814997787503</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>531.92</t>
+          <t>5.31915331541094</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>518.65</t>
+          <t>5.18649741083114</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>509.04</t>
+          <t>5.09036043587862</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>507.63</t>
+          <t>5.07627409048531</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>491.03</t>
+          <t>4.91030195688303</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>476.21</t>
+          <t>4.76208414176726</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>474.69</t>
+          <t>4.74687643318518</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>493.36</t>
+          <t>4.93363423941031</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>509.58</t>
+          <t>5.095771054953</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>491.12</t>
+          <t>4.9112407052786</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>491.99</t>
+          <t>4.91985349885342</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>280.29</t>
+          <t>2.8028710236682</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>513.6</t>
+          <t>5.13598945279718</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>541.06</t>
+          <t>5.41055822179628</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>544.27</t>
+          <t>5.44270897407481</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>514.91</t>
+          <t>5.14906259226851</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>394.28</t>
+          <t>3.94278432999498</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>384.95</t>
+          <t>3.84949448701376</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>557.67</t>
+          <t>5.57670471907425</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>539.17</t>
+          <t>5.39168346654995</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>524.51</t>
+          <t>5.24508515217908</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>521.93</t>
+          <t>5.21930235831146</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>557.72</t>
+          <t>5.57723473312356</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>537.35</t>
+          <t>5.37348934653725</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>512.42</t>
+          <t>5.12415673621264</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>520.63</t>
+          <t>5.20626601087892</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>548.03</t>
+          <t>5.48028412299204</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>541.44</t>
+          <t>5.41439994293094</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>551.7</t>
+          <t>5.51702403816985</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>531.02</t>
+          <t>5.31018801787781</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>478.13</t>
+          <t>4.7812776353724</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>479.93</t>
+          <t>4.79932642108439</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>484.1</t>
+          <t>4.84096562264134</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>412.14</t>
+          <t>4.12140350013668</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>401.19</t>
+          <t>4.0119051299689</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>390.75</t>
+          <t>3.90747600164849</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>390.06</t>
+          <t>3.90058450557726</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>409.38</t>
+          <t>4.09383886755038</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>399.16</t>
+          <t>3.99161544240371</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>383.01</t>
+          <t>3.83005988389724</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>395.39</t>
+          <t>3.95387669560603</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>364.99</t>
+          <t>3.64988772165449</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>386.79</t>
+          <t>3.86786829235368</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>386.31</t>
+          <t>3.86305543575632</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>373.07</t>
+          <t>3.73074435626734</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>344.79</t>
+          <t>3.44785065996888</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>339.43</t>
+          <t>3.39431689474338</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>338.17</t>
+          <t>3.38169405571726</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>446.8</t>
+          <t>4.46802140896115</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>436.09</t>
+          <t>4.36088894643524</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>424.28</t>
+          <t>4.24279867845913</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>419.51</t>
+          <t>4.19505905853879</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>449.2</t>
+          <t>4.49201229476407</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>440.18</t>
+          <t>4.40184914241689</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>439.23</t>
+          <t>4.39226256581069</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>450.59</t>
+          <t>4.50585034289202</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>474.48</t>
+          <t>4.7447643978093</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>449.9</t>
+          <t>4.49903518613867</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>4.57997352079924</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>452.28</t>
+          <t>4.5228265483182</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>443.57</t>
+          <t>4.43569901900444</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>4.3199774996099</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>427.37</t>
+          <t>4.27372605067974</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>405.02</t>
+          <t>4.05022651294538</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>391.73</t>
+          <t>3.91729603830543</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>380.62</t>
+          <t>3.80617703159001</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>379.48</t>
+          <t>3.79480299669212</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>395.62</t>
+          <t>3.95617496708922</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>386.79</t>
+          <t>3.86791914280354</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>374.1</t>
+          <t>3.74097609781587</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>380.42</t>
+          <t>3.80418726833754</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>396.08</t>
+          <t>3.96077730627814</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>383.05</t>
+          <t>3.83053475190408</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>382.43</t>
+          <t>3.82433245334709</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>373.91</t>
+          <t>3.7391007025716</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>360.79</t>
+          <t>3.60787844664056</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>346.64</t>
+          <t>3.46636297986745</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>359.91</t>
+          <t>3.59910883060751</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>552.83</t>
+          <t>5.52834145848592</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>533.87</t>
+          <t>5.33867192682286</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>493.83</t>
+          <t>4.93825746337353</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>540.91</t>
+          <t>5.40908411553168</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>576.03</t>
+          <t>5.76027009693659</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>563.84</t>
+          <t>5.63842732830385</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>547.91</t>
+          <t>5.4790934072946</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>581.1</t>
+          <t>5.81100579444219</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>598.43</t>
+          <t>5.98431271097315</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>589.1</t>
+          <t>5.89097156241915</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>601.5</t>
+          <t>6.01503693370601</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>586.86</t>
+          <t>5.86858592368974</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>556.43</t>
+          <t>5.56430731070377</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>558.48</t>
+          <t>5.58479450039693</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>543.47</t>
+          <t>5.4346859598746</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>448.43</t>
+          <t>4.48427441194117</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>435.91</t>
+          <t>4.35906153407907</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>425.29</t>
+          <t>4.25290032701054</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>427.23</t>
+          <t>4.27231196720371</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>449.27</t>
+          <t>4.49267290563204</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>443.78</t>
+          <t>4.43782451564672</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>432.35</t>
+          <t>4.32353501067707</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>441.53</t>
+          <t>4.41525768404414</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>396.01</t>
+          <t>3.96006788287463</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>445.3</t>
+          <t>4.4530397079433</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>447.15</t>
+          <t>4.47153899794597</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>435.52</t>
+          <t>4.35516878153266</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>419.56</t>
+          <t>4.19555720282163</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>402.2</t>
+          <t>4.0219939177866</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>400.19</t>
+          <t>4.00187397388341</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>452.71</t>
+          <t>4.52705408088139</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>440.1</t>
+          <t>4.40096911990381</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>426.91</t>
+          <t>4.26905613849181</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>433.34</t>
+          <t>4.3333959152702</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>452.82</t>
+          <t>4.52819896191953</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>446.52</t>
+          <t>4.46519699520139</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>434.46</t>
+          <t>4.34461418739588</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>446.87</t>
+          <t>4.46871744426194</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>426.43</t>
+          <t>4.26425957043942</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>444.13</t>
+          <t>4.4413222289187</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>448.24</t>
+          <t>4.48238977090572</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>437.56</t>
+          <t>4.37558379262167</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>419.26</t>
+          <t>4.19260629204403</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>402.57</t>
+          <t>4.02571883176331</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>392.09</t>
+          <t>3.92085362205685</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
